--- a/BMA_DB_Tables_CRUD.xlsx
+++ b/BMA_DB_Tables_CRUD.xlsx
@@ -15,11 +15,11 @@
     <sheet name="ლეგენდა" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ცხრილები'!$A$1:$N$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'კავშირები (FK)'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'გამოტანილი — ხედები'!$A$1:$E$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ჩამონათვალები (enum)'!$A$1:$D$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CRUD მიმოხილვა'!$A$1:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ცხრილები'!$A$1:$N$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'კავშირები (FK)'!$A$1:$I$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'გამოტანილი — ხედები'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ჩამონათვალები (enum)'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CRUD მიმოხილვა'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'ლეგენდა'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -94,12 +94,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9E7"/>
+        <fgColor rgb="FFE6F4EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4EC"/>
+        <fgColor rgb="FFFBE9E7"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,13 +172,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,10 +187,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -655,17 +655,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>venues</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>ფილიალები</t>
+          <t>აუდიტორიები და სივრცეები</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>branchesData</t>
+          <t>venuesData</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>name, address, active</t>
+          <t>code (uniq), type, capacity, active</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -705,39 +705,35 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>○ მხოლოდ ნახვა</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>ფილიალის მართვის ეკრანი მოთხოვნით მოიხსნა — ჩანაწერები მხოლოდ იკითხება</t>
-        </is>
-      </c>
+          <t>✔ სრული CRUD</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-03</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>venues</t>
+          <t>lesson_slots</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>აუდიტორიები და სივრცეები</t>
+          <t>გაკვეთილის სლოტები</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -747,7 +743,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>venuesData</t>
+          <t>slotTemplates</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -762,12 +758,12 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>code (uniq), type, capacity, active</t>
+          <t>ordinal, starts_at, ends_at</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
@@ -777,45 +773,49 @@
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✔ სრული CRUD</t>
-        </is>
-      </c>
-      <c r="N3" s="8" t="inlineStr"/>
+          <t>○ მხოლოდ ნახვა</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>სლოტების ბადე ფიქსირებულია (I–VII) — სისტემიდან არ იმართება</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>lesson_slots</t>
+          <t>programs</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>გაკვეთილის სლოტები</t>
+          <t>საგანმანათლებლო პროგრამები</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>საცნობარო</t>
+          <t>პროგრამები</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>slotTemplates</t>
+          <t>programsData</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>ordinal, starts_at, ends_at</t>
+          <t>name, name_en, type, nqf, qualification, duration_years, total_credits, status</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -845,49 +845,49 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>○ მხოლოდ ნახვა</t>
+          <t>✔ სრული CRUD</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>სლოტების ბადე ფიქსირებულია (I–VII) — სისტემიდან არ იმართება</t>
+          <t>duration_years განსაზღვრავს სასწავლო წლებს და კვირების ჯამს — ცალკე პერიოდის ცხრილი არ არსებობს</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>programs</t>
+          <t>intakes</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>საგანმანათლებლო პროგრამები</t>
+          <t>მიღებები</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>პროგრამები</t>
+          <t>მიღებები</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>programsData</t>
+          <t>intakesData</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -897,69 +897,69 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>order_id → T-41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>name, name_en, type, nqf, qualification, duration_years, total_credits, status</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
+          <t>name (uniq), season, year</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
         </is>
       </c>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>რედაქტირება მოთხოვნით ამოღებულია — დარჩა დამატება და წაშლა</t>
+          <t>წაშლა იბლოკება, თუ მიღებაზეა პროგრამა, ჯგუფი ან სტუდენტი</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-08</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>intakes</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>მიღებები</t>
+          <t>მოდულების რეესტრი</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>მიღებები</t>
+          <t>მოდულების რეესტრი</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>intakesData</t>
+          <t>moduleRegistry</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>name, season, year</t>
+          <t>title (uniq), type (theoretical | practical)</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -989,49 +989,45 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>○ მხოლოდ ნახვა</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>მიღება წინასწარ განსაზღვრულია — სისტემიდან არ იმართება</t>
-        </is>
-      </c>
+          <t>✔ სრული CRUD</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>T-06</t>
+          <t>T-10</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>study_periods</t>
+          <t>intake_programs</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>სასწავლო პერიოდები</t>
+          <t>მიღების პროგრამები</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>საცნობარო</t>
+          <t>მიღებები</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>studyYearsData</t>
+          <t>intakePrograms</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1041,141 +1037,137 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>intake_id → T-05</t>
+          <t>intake_id → T-05, program_id → T-04</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>starts_on</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>პერიოდის ეკრანი მოთხოვნით მოიხსნა; დასრულება კვირებიდან ითვლება (T-07)</t>
+          <t>რედაქტირება არ არის — ბმა ემატება და იხსნება</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>study_period_weeks</t>
+          <t>intake_modules</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>პერიოდის კვირები</t>
+          <t>მიღების მოდულები</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>საცნობარო</t>
+          <t>მიღებები</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>periodWeeks</t>
+          <t>intakeModules</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>(period_id, program_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>period_id → T-06, program_id → T-04</t>
+          <t>intake_program_id → T-10, module_id → T-08, teacher_id → T-18</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>weeks</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>დამატება/რედაქტირება არ არის — ეკრანი მოთხოვნით მოიხსნა</t>
-        </is>
-      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>T-08</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>intake_module_weeks</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>მოდულების რეესტრი</t>
+          <t>მოდულის კვირეული საათები</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>მოდულების რეესტრი</t>
+          <t>მიღებები → საათები</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>moduleRegistry</t>
+          <t>intakeModuleWeeks</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1185,35 +1177,35 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>intake_module_id → T-11</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>title (uniq), type (theoretical | practical)</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
+          <t>week (uniq/მოდულზე), contact_h, self_h, assess_h</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>✔ სრული CRUD</t>
         </is>
@@ -1223,27 +1215,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>T-09</t>
+          <t>T-13</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>module_outcomes</t>
+          <t>module_prerequisites</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>მოდულის სწავლის შედეგები</t>
+          <t>მოდულის წინაპირობები</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>მოდულების რეესტრი</t>
+          <t>მიღებები</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>templateOutcomes</t>
+          <t>modulePrereqs</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1253,69 +1245,69 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>module_id → T-08</t>
+          <t>prereq_intake_module_id → T-11, dependent_intake_module_id → T-11</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>no, title, direction, contact_h, self_h, assess_h</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>შედეგების რედაქტორი ინტერფეისში არ არის — ჩანაწერები მხოლოდ იკითხება</t>
+          <t>რედაქტირება არ არის — წყვილი იშლება და ხელახლა ემატება</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>T-10</t>
+          <t>T-14</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>intake_programs</t>
+          <t>partner_organisations</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>მიღების პროგრამები</t>
+          <t>პარტნიორი ორგანიზაციები</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>მიღებები</t>
+          <t>პარტნიორი ორგანიზაციები</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>intakePrograms</t>
+          <t>partnersData</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -1325,69 +1317,65 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>intake_id → T-05, program_id → T-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>რედაქტირება არ არის — ბმა ემატება და იხსნება</t>
-        </is>
-      </c>
+          <t>name (uniq), agreement_no, agreement_date, kind, active</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-15</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>intake_modules</t>
+          <t>partner_teachers</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>მიღების მოდულები</t>
+          <t>ორგანიზაციის მასწავლებლები</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>მიღებები</t>
+          <t>პარტნიორი ორგანიზაციები</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>intakeModules</t>
+          <t>partnerTeachers</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1397,35 +1385,35 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>intake_program_id → T-10, module_id → T-08, teacher_id → T-19</t>
+          <t>partner_id → T-14</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
+          <t>name, spec, phone, active</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>✔ სრული CRUD</t>
         </is>
@@ -1435,27 +1423,27 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>intake_module_weeks</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>მოდულის კვირეული საათები</t>
+          <t>როლები</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>მიღებები → საათები</t>
+          <t>მომხმარებლები და როლები</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>intakeModuleWeeks</t>
+          <t>rolesData</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1465,87 +1453,91 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>intake_module_id → T-11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>week (uniq/მოდულზე), contact_h, self_h, assess_h</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
+          <t>label, scope, ui, predefined, special</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>✔ სრული CRUD</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>ორი წინასწარ განსაზღვრული როლი არ იშლება</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>module_prerequisites</t>
+          <t>role_permissions</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>მოდულის წინაპირობები</t>
+          <t>როლის CRUD წვდომები</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>მიღებები</t>
+          <t>მომხმარებლები და როლები</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>modulePrereqs</t>
+          <t>rolePermissions</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(role_id, resource, op)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>prereq_intake_module_id → T-11, dependent_intake_module_id → T-11</t>
+          <t>role_id → T-16</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
+          <t>resource (26), op (c|r|u|d), allowed</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
           <t>✔</t>
@@ -1553,14 +1545,14 @@
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
           <t>◐ ნაწილობრივი</t>
@@ -1568,34 +1560,34 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>რედაქტირება არ არის — წყვილი იშლება და ხელახლა ემატება</t>
+          <t>ცალკე ჩანაწერი არ იქმნება/იშლება — მატრიცა როლთან ერთად არსებობს</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>partner_organisations</t>
+          <t>users</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>პარტნიორი ორგანიზაციები</t>
+          <t>მომხმარებლები</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>პარტნიორი ორგანიზაციები</t>
+          <t>მომხმარებლები და როლები</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>partnersData</t>
+          <t>usersData</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1605,65 +1597,69 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
+          <t>role_id → T-16, group_id → T-22, program_id → T-04, intake_id → T-05</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>name, email, phone, status; როლისთვის სპეციფიკური: dept | implementer_type, spec, modules, work_started_on, qualification | study_year, balance, has_sen, social_status, legal_rep_*, suspension_*, termination_*</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>name (uniq), agreement_no, agreement_date, kind, active</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>ერთიანი ცხრილი — ინტერფეისი განისაზღვრება როლით (student / teacher / admin). წაშლა არ არის: სტატუსი იცვლება ან ჩანაწერი დეაქტივირდება</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T-15</t>
+          <t>T-21</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>partner_teachers</t>
+          <t>student_files</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>ორგანიზაციის მასწავლებლები</t>
+          <t>სტუდენტის ფაილები</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>პარტნიორი ორგანიზაციები</t>
+          <t>სტუდენტის პროფილი</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>partnerTeachers</t>
+          <t>studentFilesData</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1673,12 +1669,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>partner_id → T-14</t>
+          <t>student_id → T-18</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>name, spec, phone, active</t>
+          <t>name, uploaded_on</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1708,34 +1704,34 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>რედაქტირება არ არის — ჩანაწერი ემატება და იხსნება</t>
+          <t>რედაქტირება არ არის — ფაილი მიემაგრება და მოიხსნება</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>როლები</t>
+          <t>ჯგუფები</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>მომხმარებლები და როლები</t>
+          <t>ჯგუფები</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>rolesData</t>
+          <t>groupsData</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -1745,106 +1741,106 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>program_id → T-04, intake_id → T-05</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>label, scope, ui, predefined, special</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
+          <t>name, study_year, students, active</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>✔ სრული CRUD</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>ორი წინასწარ განსაზღვრული როლი არ იშლება</t>
+          <t>წაშლა იბლოკება, თუ ჯგუფშია სტუდენტი, მოდული ან ხელახლა გავლის ჩანაწერი</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>role_permissions</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>როლის CRUD წვდომები</t>
+          <t>მოდულის ინსტანციები</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>მომხმარებლები და როლები</t>
+          <t>ჯგუფის მოდულები</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>rolePermissions</t>
+          <t>modulesData</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>(role_id, resource, op)</t>
+          <t>code</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>role_id → T-16</t>
+          <t>module_id → T-08, group_id → T-22, program_id → T-04, intake_id → T-05, teacher_id → T-18</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>resource (26), op (c|r|u|d), allowed</t>
+          <t>name, reg_no, study_year, credits, starts_on, ends_on</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
           <t>◐ ნაწილობრივი</t>
@@ -1852,34 +1848,34 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>ცალკე ჩანაწერი არ იქმნება/იშლება — მატრიცა როლთან ერთად არსებობს</t>
+          <t>წაშლა არ არის — ინსტანცია ისტორიულ ჩანაწერად რჩება</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-24</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>admin_users</t>
+          <t>module_sessions</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>ადმინისტრაციული მომხმარებლები</t>
+          <t>მოდულის საათები (ლექცია / შეფასება)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>მომხმარებლები და როლები</t>
+          <t>ელექტრონული ჟურნალი</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>admins</t>
+          <t>moduleLectures + generated ids</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1889,17 +1885,17 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>role_id → T-16</t>
+          <t>module_instance_id → T-23</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>name, dept, email, phone, status</t>
+          <t>week, kind (lecture | assessment), ordinal, title, duration_min, conducted, conducted_on, note</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
@@ -1924,34 +1920,34 @@
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>წაშლა არ არის — მომხმარებელი დეაქტივირდება</t>
+          <t>ცხრილი საჭიროა დასწრებისა და შეფასების FK-ისთვის; ID გენერირდება კვირეული განაწილებიდან, ხელით არ იქმნება</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-26</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>teachers</t>
+          <t>module_materials</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>პროფ. განათლების მასწავლებლები</t>
+          <t>მოდულის სასწავლო მასალები</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>მასწავლებლები</t>
+          <t>ჩემი სასწავლო მოდულები</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>teachers</t>
+          <t>moduleMaterials</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1961,12 +1957,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>branch_id → T-01, appoint_order_id → T-41</t>
+          <t>module_instance_id → T-23, library_document_id → T-28</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>name, implementer_type, spec, email, phone, work_started_on, qualification, status</t>
+          <t>type, title, source</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -1981,12 +1977,12 @@
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
@@ -1996,34 +1992,34 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>წაშლა არ არის — არქივდება სტატუსით</t>
+          <t>რედაქტირება არ არის — მასალა ემატება და მოიხსნება</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>schedule_entries</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>პროფესიული სტუდენტები</t>
+          <t>განრიგის ჩანაწერები</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>პროფესიული სტუდენტები</t>
+          <t>განრიგი</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>schedPlacements</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2033,12 +2029,12 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>branch_id → T-01, group_id → T-23, program_id → T-04, intake_id → T-05, enrol_order_id → T-41, suspension_order_id → T-41</t>
+          <t>venue_id → T-02, slot_id → T-03, group_id → T-22, intake_module_id → T-11</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>name, study_year, balance, status, email, phone, has_sen, social_status, legal_rep_name, legal_rep_relation, legal_rep_phone, suspended_on, suspension_reason, suspension_expires_on</t>
+          <t>week, day</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -2053,12 +2049,12 @@
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
@@ -2068,106 +2064,106 @@
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>წაშლა არ არის — სტატუსი იცვლება ბრძანებით (შეჩერება / შეწყვეტა)</t>
+          <t>რედაქტირება არ არის — საათი მოიხსნება და ხელახლა თავსდება</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>T-21</t>
+          <t>T-28</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>student_files</t>
+          <t>library_documents</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>სტუდენტის ფაილები</t>
+          <t>ბიბლიოთეკის ელ. დოკუმენტები</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>სტუდენტის პროფილი</t>
+          <t>ბიბლიოთეკა</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>studentFilesData</t>
+          <t>libraryData</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isbn</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>student_id → T-20</t>
+          <t>module_instance_id → T-23</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>name, uploaded_on</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
+          <t>title, author, cat, url</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>რედაქტირება არ არის — ფაილი მიემაგრება და მოიხსნება</t>
+          <t>ბეჭდური წიგნები ცხრილში არ ინახება — გარე პლატფორმის კატალოგი</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-29</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>practice_placements</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>ჯგუფები</t>
+          <t>პრაქტიკის განაწილება</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>ჯგუფები</t>
+          <t>მიღებები → კლინიკები</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>groupsData</t>
+          <t>practicePlacements</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -2177,131 +2173,127 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>branch_id → T-01, program_id → T-04, intake_id → T-05</t>
+          <t>intake_module_id → T-11, student_id → T-18, partner_id → T-14, partner_teacher_id → T-15</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>name, study_year, students, active</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N23" s="8" t="inlineStr">
-        <is>
-          <t>წაშლა არ არის — ჯგუფი დეაქტივირდება; სასწავლო წელი ავტომატურად იხურება</t>
-        </is>
-      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-30</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>module_instances</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>მოდულის ინსტანციები</t>
+          <t>დასწრების აღრიცხვა</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ჯგუფის მოდულები</t>
+          <t>ელექტრონული ჟურნალი</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>modulesData</t>
+          <t>ejAtt / sessionAtt / myAttendance</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>(session_id, student_id)</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>module_id → T-08, group_id → T-22, program_id → T-04, intake_id → T-05, teacher_id → T-19, branch_id → T-01</t>
+          <t>session_id → T-24, student_id → T-18</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>name, reg_no, study_year, credits, starts_on, ends_on</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
+          <t>status (present | absent), marked_by, marked_at</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>წაშლა არ არის — ინსტანცია ისტორიულ ჩანაწერად რჩება</t>
+          <t>ადმინი და ლექტორი — სრული CRUD; სტუდენტი მხოლოდ ნახულობს</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-31</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>module_sessions</t>
+          <t>session_outcomes</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>მოდულის საათები (ლექცია / შეფასება)</t>
+          <t>შეფასების შედეგები საათზე</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2311,79 +2303,79 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>moduleLectures + generated ids</t>
+          <t>ejOut / sessionOut</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(session_id, student_id)</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>module_instance_id → T-23, intake_module_week_id → T-12, outcome_id → T-09</t>
+          <t>session_id → T-24, student_id → T-18</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>week, kind (lecture | assessment), ordinal, title, duration_min, conducted, conducted_on, note</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
+          <t>result (confirmed | not_confirmed), marked_by, marked_at</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>ცხრილი საჭიროა დასწრებისა და შეფასების FK-ისთვის; wireframe-ში ID გენერირდება კვირეული განაწილებიდან, ხელით არ იქმნება</t>
+          <t>ადმინი და ლექტორი — სრული CRUD; სტუდენტი მხოლოდ ნახულობს</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>T-25</t>
+          <t>T-33</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>session_materials</t>
+          <t>reassessments</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>საათის მასალები</t>
+          <t>გადაბარებები</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>მოდულის დეტალები</t>
+          <t>სწავლის შედეგები</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>lectureMaterials</t>
+          <t>reassessments</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2393,12 +2385,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>session_id → T-24</t>
+          <t>student_id → T-18, module_instance_id → T-23, intake_module_id → T-11, group_id → T-22</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>type, title, file_url, link, downloadable</t>
+          <t>outcome_no, attempt_no (≤2), fee_paid, scheduled_on, due_on, status</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -2413,14 +2405,14 @@
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L26" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
           <t>◐ ნაწილობრივი</t>
@@ -2428,34 +2420,34 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>რედაქტირება არ არის — მასალა ემატება და მოიხსნება</t>
+          <t>წაშლა არ არის — ცდების ისტორია ინახება</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>T-26</t>
+          <t>T-34</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>module_materials</t>
+          <t>module_repeats</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>მოდულის სასწავლო მასალები</t>
+          <t>მოდულის ხელახლა გავლა</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>ჩემი სასწავლო მოდულები</t>
+          <t>სწავლის შედეგები</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>moduleMaterials</t>
+          <t>moduleRepeats</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -2465,12 +2457,12 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>module_instance_id → T-23, library_document_id → T-28</t>
+          <t>student_id → T-18, module_instance_id → T-23, intake_module_id → T-11, failed_in_group_id → T-22, repeat_with_group_id → T-22</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>type, title, source</t>
+          <t>outcome_no, decided_on, status</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -2485,14 +2477,14 @@
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
           <t>◐ ნაწილობრივი</t>
@@ -2500,34 +2492,34 @@
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>რედაქტირება არ არის — მასალა ემატება და მოიხსნება</t>
+          <t>წაშლა არ არის — ბრძანებით გაფორმებული ჩანაწერი ინახება</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>T-27</t>
+          <t>T-40</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>schedule_entries</t>
+          <t>audit_log</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>განრიგის ჩანაწერები</t>
+          <t>აუდიტის ჟურნალი</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>განრიგი</t>
+          <t>სისტემა</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>schedPlacements</t>
+          <t>auditLog</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2537,12 +2529,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>venue_id → T-02, slot_id → T-03, group_id → T-22, intake_module_id → T-11</t>
+          <t>actor_id → T-18</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>week, day</t>
+          <t>actor, role, action, entity, entity_id, at, ip</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -2562,7 +2554,7 @@
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
@@ -2572,106 +2564,106 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>რედაქტირება არ არის — საათი მოიხსნება და ხელახლა თავსდება</t>
+          <t>უცვლელი ჟურნალი — ჩანაწერი მხოლოდ ემატება; ეკრანი მოთხოვნით მოიხსნა</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>T-28</t>
+          <t>T-41</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>library_documents</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>ბიბლიოთეკის ელ. დოკუმენტები</t>
+          <t>ბრძანებები</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>ბიბლიოთეკა</t>
+          <t>ბრძანებები</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>libraryData</t>
+          <t>ordersData</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>isbn</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>module_instance_id → T-23</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>title, author, cat, url</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
+          <t>no, date, index (01 | 02), subject, file_url</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>ბეჭდური წიგნები ცხრილში არ ინახება — გარე პლატფორმის კატალოგი</t>
+          <t>ბრძანება მხოლოდ აიტვირთება და იკითხება — სისტემაში სხვა ჩანაწერს არ ებმევა, არაფრის წინაპირობა არ არის</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>T-29</t>
+          <t>T-42</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>practice_placements</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>პრაქტიკის განაწილება</t>
+          <t>გადახდები</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>მიღებები → კლინიკები</t>
+          <t>გადახდები</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>practicePlacements</t>
+          <t>paymentsData</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2681,209 +2673,209 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>intake_module_id → T-11, student_id → T-20, partner_id → T-14, partner_teacher_id → T-15</t>
+          <t>student_id → T-18</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
+          <t>amount, paid, due, status, method</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>წაშლა არ არის — ფინანსური ჩანაწერი ინახება</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>T-30</t>
+          <t>T-43</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>attendance</t>
+          <t>applications</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>დასწრების აღრიცხვა</t>
+          <t>განაცხადები</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>ელექტრონული ჟურნალი</t>
+          <t>განაცხადები</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>ejAtt / sessionAtt / myAttendance</t>
+          <t>appsData</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>(session_id, student_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>session_id → T-24, student_id → T-20</t>
+          <t>student_id → T-18</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>status (present | absent), marked_by, marked_at</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
+          <t>type, desc, date, status</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>ადმინი და ლექტორი — სრული CRUD; სტუდენტი მხოლოდ ნახულობს</t>
+          <t>სტუდენტი ქმნის, ადმინი ამტკიცებს; წაშლა არ არის</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>T-31</t>
+          <t>T-44</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>session_outcomes</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>შეფასების შედეგები საათზე</t>
+          <t>სიახლეები</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>ელექტრონული ჟურნალი</t>
+          <t>სიახლეები</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ejOut / sessionOut</t>
+          <t>newsAdminData</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>(session_id, student_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>session_id → T-24, student_id → T-20</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>result (confirmed | not_confirmed), marked_by, marked_at</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr">
+          <t>tag, title, date, status, body, img</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>✔ სრული CRUD</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>ადმინი და ლექტორი — სრული CRUD; სტუდენტი მხოლოდ ნახულობს</t>
-        </is>
-      </c>
+      <c r="N32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>T-32</t>
+          <t>T-45</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>outcome_results</t>
+          <t>surveys</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>სწავლის შედეგის ჩანაწერი</t>
+          <t>გამოკითხვები</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>სწავლის შედეგები</t>
+          <t>გამოკითხვები</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>outcomeResults</t>
+          <t>surveysAdminData</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -2893,17 +2885,17 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>student_id → T-20, module_instance_id → T-23, outcome_id → T-09, register_id → T-36</t>
+          <t>module_instance_id → T-23</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>outcome_no, result, attempt_no, assessed_on, direction, source</t>
+          <t>title, target, url, status, responses</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2913,49 +2905,49 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>○ მხოლოდ ნახვა</t>
+          <t>✔ სრული CRUD</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>კრედიტის სისტემა-ჩანაწერი — იწერება შეფასების საათიდან (T-31), ხელით არ იქმნება</t>
+          <t>ბმული ჩანს მხოლოდ მოდულის დასრულების შემდეგ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>T-33</t>
+          <t>T-46</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>reassessments</t>
+          <t>job_vacancies</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>გადაბარებები</t>
+          <t>ვაკანსიები</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>სწავლის შედეგები</t>
+          <t>კარიერა</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>reassessments</t>
+          <t>jobsAdminData</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2965,69 +2957,65 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>student_id → T-20, module_instance_id → T-23, intake_module_id → T-11, group_id → T-22, order_id → T-41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>outcome_no, attempt_no (≤2), fee_paid, scheduled_on, due_on, status</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>წაშლა არ არის — ცდების ისტორია ინახება</t>
-        </is>
-      </c>
+          <t>title, org, kind, deadline, status, applicants</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>T-34</t>
+          <t>T-47</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>module_repeats</t>
+          <t>clubs</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>მოდულის ხელახლა გავლა</t>
+          <t>კლუბები</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>სწავლის შედეგები</t>
+          <t>კლუბები</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>moduleRepeats</t>
+          <t>clubsAdminData</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -3037,69 +3025,65 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>student_id → T-20, module_instance_id → T-23, intake_module_id → T-11, failed_in_group_id → T-22, repeat_with_group_id → T-22, order_id → T-41</t>
+          <t>lead_teacher_id → T-18</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>outcome_no, decided_on, status</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t>წაშლა არ არის — ბრძანებით გაფორმებული ჩანაწერი ინახება</t>
-        </is>
-      </c>
+          <t>icon, name (uniq), desc, members, active</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>✔ სრული CRUD</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>T-35</t>
+          <t>T-48</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>assessment_instruments</t>
+          <t>club_events</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>შეფასების ინსტრუმენტები</t>
+          <t>კლუბის ღონისძიებები</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>მოდულის დეტალები</t>
+          <t>კლუბები</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>instrumentsData</t>
+          <t>clubEvents</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3109,1043 +3093,119 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>module_instance_id → T-23, outcome_id → T-09</t>
+          <t>club_id → T-47</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>status, reject_reason</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
+          <t>title, on</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>ვალიდაცია სისტემის გარეთ ხდება</t>
+          <t>რედაქტირება არ არის — ღონისძიება ემატება და იშლება</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>T-36</t>
+          <t>T-49</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>registers</t>
+          <t>club_members</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>უწყისები</t>
+          <t>კლუბის წევრობა</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>სწავლის შედეგები</t>
+          <t>კლუბები</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>registersData</t>
+          <t>clubsData.joined</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(club_id, student_id)</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>module_instance_id → T-23, teacher_id → T-19</t>
+          <t>club_id → T-47, student_id → T-18</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>compiled_on, due_on, signed_at, journal_no</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
+          <t>joined_on</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>◐ ნაწილობრივი</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>უწყისის ეკრანი მოთხოვნით მოიხსნა; ხელმოწერა სისტემის გარეთ</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>T-37</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>interim_assessments</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>შუალედური შეფასებები</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>შუალედური შეფასება</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>interimData</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>program_id → T-04, group_id → T-22, order_id → T-41</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>held_on, task_type, percent_done, commission, participated, total</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>მხოლოდ ნახვა</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>T-38</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>individual_study_plans</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>ინდივიდუალური სასწ. გეგმები</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>სტუდენტის პროფილი</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>ispData</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>student_id → T-20, order_id → T-41</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>ground, kind</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t>მხოლოდ ნახვა</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>T-39</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>appeals</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>აპელაციები</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>სწავლის შედეგები</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>appealsData</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>student_id → T-20, module_instance_id → T-23</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>filed_on, status</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>მხოლოდ ნახვა</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>T-40</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>audit_log</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>აუდიტის ჟურნალი</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>სისტემა</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>auditLog</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>actor_id → T-18</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>actor, role, action, entity, entity_id, at, ip</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>უცვლელი ჟურნალი — ჩანაწერი მხოლოდ ემატება; ეკრანი მოთხოვნით მოიხსნა</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>T-41</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>ბრძანებები</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>ბრძანებები</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>ordersData</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>amends_order_id → T-41</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>no, date, index (01 | 02), subject, eflow, e_sign, p_sign</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>○ მხოლოდ ნახვა</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>ფორმა ივსება, მაგრამ ჩანაწერი არ ინახება (მხოლოდ ტოსტი); ცვლილება = ახალი ბრძანება, წაშლა დაუშვებელია</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>T-42</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>payments</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>გადახდები</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>გადახდები</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>paymentsData</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>student_id → T-20</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>amount, paid, due, status, method</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L43" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>წაშლა არ არის — ფინანსური ჩანაწერი ინახება</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>T-43</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>applications</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>განაცხადები</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>განაცხადები</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>appsData</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>student_id → T-20</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>type, desc, date, status</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>სტუდენტი ქმნის, ადმინი ამტკიცებს; წაშლა არ არის</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>T-44</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>სიახლეები</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>სიახლეები</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>newsAdminData</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>tag, title, date, status, body, img</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
-        </is>
-      </c>
-      <c r="N45" s="8" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>T-45</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>surveys</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>გამოკითხვები</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>გამოკითხვები</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>surveysAdminData</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>module_instance_id → T-23</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>title, target, url, status, responses</t>
-        </is>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K46" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
-        </is>
-      </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>ბმული ჩანს მხოლოდ მოდულის დასრულების შემდეგ</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>T-46</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>job_vacancies</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>ვაკანსიები</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>კარიერა</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>jobsAdminData</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>title, org, kind, deadline, status, applicants</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M47" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
-        </is>
-      </c>
-      <c r="N47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>T-47</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>clubs</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>კლუბები</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>კლუბები</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>clubsAdminData</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>lead_teacher_id → T-19</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>icon, name (uniq), desc, members, active</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M48" s="9" t="inlineStr">
-        <is>
-          <t>✔ სრული CRUD</t>
-        </is>
-      </c>
-      <c r="N48" s="4" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>T-48</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>club_events</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>კლუბის ღონისძიებები</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>კლუბები</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>clubEvents</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>club_id → T-47</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>title, on</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J49" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K49" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L49" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M49" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N49" s="8" t="inlineStr">
-        <is>
-          <t>რედაქტირება არ არის — ღონისძიება ემატება და იშლება</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>T-49</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>club_members</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>კლუბის წევრობა</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>კლუბები</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>clubsData.joined</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>(club_id, student_id)</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>club_id → T-47, student_id → T-20</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>joined_on</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L50" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="M50" s="10" t="inlineStr">
-        <is>
-          <t>◐ ნაწილობრივი</t>
-        </is>
-      </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
           <t>სტუდენტი უერთდება და გამოდის; ადმინის ინტერფეისში წევრობა მხოლოდ რაოდენობით ჩანს</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N50"/>
+  <autoFilter ref="A1:N37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4156,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4428,12 +3488,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>teachers</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -4448,7 +3508,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>პრაქტიკულ მოდულზე NULL — ლექტორი არ ეთითება</t>
+          <t>ლექტორი (role = teacher); პრაქტიკულ მოდულზე NULL</t>
         </is>
       </c>
     </row>
@@ -4601,27 +3661,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>T-09</t>
+          <t>T-15</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>module_outcomes</t>
+          <t>partner_teachers</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>module_id</t>
+          <t>partner_id</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>T-08</t>
+          <t>T-14</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>partner_organisations</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -4636,7 +3696,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>მოდულის სწავლის შედეგები</t>
+          <t>ორგანიზაციის მასწავლებლები</t>
         </is>
       </c>
     </row>
@@ -4648,27 +3708,27 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>T-06</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>study_periods</t>
+          <t>role_permissions</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>intake_id</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>intakes</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -4683,7 +3743,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>პერიოდი მიღებაზე</t>
+          <t>როლის წვდომების მატრიცა</t>
         </is>
       </c>
     </row>
@@ -4695,27 +3755,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>study_period_weeks</t>
+          <t>users</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>period_id</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>T-06</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>study_periods</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -4725,12 +3785,12 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>პერიოდის კვირები</t>
+          <t>მომხმარებელს ერთი როლი — როლი განსაზღვრავს ინტერფეისს</t>
         </is>
       </c>
     </row>
@@ -4742,27 +3802,27 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>study_period_weeks</t>
+          <t>users</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>program_id</t>
+          <t>group_id</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>programs</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -4772,12 +3832,12 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>კვირები პროგრამაზე</t>
+          <t>სტუდენტი ერთ ჯგუფში (role = student)</t>
         </is>
       </c>
     </row>
@@ -4789,27 +3849,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>T-15</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>partner_teachers</t>
+          <t>users</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>partner_id</t>
+          <t>program_id</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>partner_organisations</t>
+          <t>programs</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -4819,12 +3879,12 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>ორგანიზაციის მასწავლებლები</t>
+          <t>სტუდენტის პროგრამა</t>
         </is>
       </c>
     </row>
@@ -4836,27 +3896,27 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>role_permissions</t>
+          <t>users</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>intake_id</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>intakes</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -4866,12 +3926,12 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>როლის წვდომების მატრიცა</t>
+          <t>სტუდენტის მიღება</t>
         </is>
       </c>
     </row>
@@ -4883,27 +3943,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>T-21</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>student_files</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>admin_users</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>role_id</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>T-16</t>
-        </is>
-      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -4913,12 +3973,12 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>მომხმარებელს ერთი როლი</t>
+          <t>სტუდენტის ფაილები</t>
         </is>
       </c>
     </row>
@@ -4930,27 +3990,27 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>teachers</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>branch_id</t>
+          <t>program_id</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>programs</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -4965,7 +4025,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>მასწავლებელი ფილიალში</t>
+          <t>ჯგუფის პროგრამა</t>
         </is>
       </c>
     </row>
@@ -4977,27 +4037,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>teachers</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>appoint_order_id</t>
+          <t>intake_id</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>T-41</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>intakes</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -5012,7 +4072,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>დანიშვნა ბრძანებით</t>
+          <t>ჯგუფის მიღება</t>
         </is>
       </c>
     </row>
@@ -5024,27 +4084,27 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>group_id</t>
+          <t>module_id</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-08</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -5059,7 +4119,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>სტუდენტი ერთ ჯგუფში</t>
+          <t>ინსტანცია რეესტრის მოდულზე</t>
         </is>
       </c>
     </row>
@@ -5071,27 +4131,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>program_id</t>
+          <t>group_id</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>programs</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -5106,7 +4166,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>სტუდენტის პროგრამა</t>
+          <t>ჯგუფი გაივლის მოდულს</t>
         </is>
       </c>
     </row>
@@ -5118,27 +4178,27 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>intake_id</t>
+          <t>program_id</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>intakes</t>
+          <t>programs</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -5153,7 +4213,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>სტუდენტის მიღება</t>
+          <t>ინსტანციის პროგრამა</t>
         </is>
       </c>
     </row>
@@ -5165,27 +4225,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>enrol_order_id</t>
+          <t>intake_id</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>T-41</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>intakes</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -5200,7 +4260,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>ჩარიცხვა ბრძანებით</t>
+          <t>ინსტანციის მიღება</t>
         </is>
       </c>
     </row>
@@ -5212,27 +4272,27 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>suspension_order_id</t>
+          <t>teacher_id</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>T-41</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -5247,7 +4307,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>სტატუსის შეჩერება ბრძანებით</t>
+          <t>მოდულის ლექტორი</t>
         </is>
       </c>
     </row>
@@ -5259,27 +4319,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>T-21</t>
+          <t>T-24</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>student_files</t>
+          <t>module_sessions</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>module_instance_id</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -5294,7 +4354,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>სტუდენტის ფაილები</t>
+          <t>მოდულის საათები</t>
         </is>
       </c>
     </row>
@@ -5306,27 +4366,27 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-26</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>module_materials</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>program_id</t>
+          <t>module_instance_id</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>programs</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -5336,12 +4396,12 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>ჯგუფის პროგრამა</t>
+          <t>მასალა ებმევა მოდულს, არა ცალკეულ საათს</t>
         </is>
       </c>
     </row>
@@ -5353,27 +4413,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-26</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>module_materials</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>intake_id</t>
+          <t>library_document_id</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-28</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>intakes</t>
+          <t>library_documents</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -5383,12 +4443,12 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>SET NULL</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>ჯგუფის მიღება</t>
+          <t>ბიბლიოთეკის დოკუმენტის მიბმა</t>
         </is>
       </c>
     </row>
@@ -5400,27 +4460,27 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>schedule_entries</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>branch_id</t>
+          <t>venue_id</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>venues</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -5435,7 +4495,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>ჯგუფი ფილიალში</t>
+          <t>აუდიტორია ვერ იშლება, თუ განრიგშია</t>
         </is>
       </c>
     </row>
@@ -5447,27 +4507,27 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>module_instances</t>
+          <t>schedule_entries</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>module_id</t>
+          <t>slot_id</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>T-08</t>
+          <t>T-03</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>lesson_slots</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -5482,7 +4542,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>ინსტანცია რეესტრის მოდულზე</t>
+          <t>სლოტი × აუდიტორია</t>
         </is>
       </c>
     </row>
@@ -5494,12 +4554,12 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>module_instances</t>
+          <t>schedule_entries</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -5524,12 +4584,12 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>ჯგუფი გაივლის მოდულს</t>
+          <t>ჯგუფი ერთ საათზე ერთხელ (uniq)</t>
         </is>
       </c>
     </row>
@@ -5541,27 +4601,27 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>module_instances</t>
+          <t>schedule_entries</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>teacher_id</t>
+          <t>intake_module_id</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>teachers</t>
+          <t>intake_modules</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -5571,12 +4631,12 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>მოდულის ლექტორი</t>
+          <t>საათი მოდულის განაწილებიდან</t>
         </is>
       </c>
     </row>
@@ -5588,12 +4648,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-28</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>module_sessions</t>
+          <t>library_documents</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -5618,12 +4678,12 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>SET NULL</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>მოდულის საათები</t>
+          <t>დოკუმენტი მოდულზე</t>
         </is>
       </c>
     </row>
@@ -5635,27 +4695,27 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-29</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>module_sessions</t>
+          <t>practice_placements</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>intake_module_week_id</t>
+          <t>intake_module_id</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>intake_module_weeks</t>
+          <t>intake_modules</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -5670,7 +4730,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>საათი კვირეული განაწილებიდან</t>
+          <t>პრაქტიკული მოდული</t>
         </is>
       </c>
     </row>
@@ -5682,27 +4742,27 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-29</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>module_sessions</t>
+          <t>practice_placements</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>outcome_id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>T-09</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>module_outcomes</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -5712,12 +4772,12 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>შეფასების საათი სწავლის შედეგზე</t>
+          <t>სტუდენტი ნაწილდება კლინიკაში</t>
         </is>
       </c>
     </row>
@@ -5729,27 +4789,27 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>T-25</t>
+          <t>T-29</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>session_materials</t>
+          <t>practice_placements</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>partner_id</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-14</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>module_sessions</t>
+          <t>partner_organisations</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -5759,12 +4819,12 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>საათის მასალა</t>
+          <t>ორგანიზაცია ვერ იშლება, თუ სტუდენტია</t>
         </is>
       </c>
     </row>
@@ -5776,27 +4836,27 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>T-26</t>
+          <t>T-29</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>module_materials</t>
+          <t>practice_placements</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>module_instance_id</t>
+          <t>partner_teacher_id</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-15</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>module_instances</t>
+          <t>partner_teachers</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -5806,12 +4866,12 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>მოდულის მასალა</t>
+          <t>მასწავლებელი უნდა იყოს იმავე ორგანიზაციიდან (CHECK)</t>
         </is>
       </c>
     </row>
@@ -5823,27 +4883,27 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>T-26</t>
+          <t>T-30</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>module_materials</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>library_document_id</t>
+          <t>session_id</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>T-28</t>
+          <t>T-24</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>library_documents</t>
+          <t>module_sessions</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -5853,12 +4913,12 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>ბიბლიოთეკის დოკუმენტის მიბმა</t>
+          <t>დასწრება საათზე</t>
         </is>
       </c>
     </row>
@@ -5870,27 +4930,27 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>T-27</t>
+          <t>T-30</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>schedule_entries</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>venue_id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>venues</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -5900,12 +4960,12 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>აუდიტორია ვერ იშლება, თუ განრიგშია</t>
+          <t>სტუდენტის დასწრება</t>
         </is>
       </c>
     </row>
@@ -5917,27 +4977,27 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>T-27</t>
+          <t>T-31</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>schedule_entries</t>
+          <t>session_outcomes</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>slot_id</t>
+          <t>session_id</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>T-24</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>lesson_slots</t>
+          <t>module_sessions</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -5947,12 +5007,12 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>სლოტი × აუდიტორია</t>
+          <t>შეფასების საათი</t>
         </is>
       </c>
     </row>
@@ -5964,27 +5024,27 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>T-27</t>
+          <t>T-31</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>schedule_entries</t>
+          <t>session_outcomes</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>group_id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -5999,7 +5059,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>ჯგუფი ერთ საათზე ერთხელ (uniq)</t>
+          <t>სტუდენტის შეფასება</t>
         </is>
       </c>
     </row>
@@ -6011,27 +5071,27 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>T-27</t>
+          <t>T-33</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>schedule_entries</t>
+          <t>reassessments</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>intake_module_id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>intake_modules</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -6046,7 +5106,7 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>საათი მოდულის განაწილებიდან</t>
+          <t>გადაბარება სტუდენტზე</t>
         </is>
       </c>
     </row>
@@ -6058,12 +5118,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>T-28</t>
+          <t>T-33</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>library_documents</t>
+          <t>reassessments</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -6088,12 +5148,12 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>დოკუმენტი მოდულზე</t>
+          <t>გადაბარება მოდულზე</t>
         </is>
       </c>
     </row>
@@ -6105,12 +5165,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>T-29</t>
+          <t>T-33</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>practice_placements</t>
+          <t>reassessments</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -6135,12 +5195,12 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>პრაქტიკული მოდული</t>
+          <t>შეფასების საათები განაწილებიდან</t>
         </is>
       </c>
     </row>
@@ -6152,27 +5212,27 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>T-29</t>
+          <t>T-33</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>practice_placements</t>
+          <t>reassessments</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>group_id</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -6182,12 +5242,12 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>სტუდენტი ნაწილდება კლინიკაში</t>
+          <t>საკუთარი ჯგუფი — გადაბარება ჯგუფს არ ცვლის</t>
         </is>
       </c>
     </row>
@@ -6199,27 +5259,27 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>T-29</t>
+          <t>T-34</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>practice_placements</t>
+          <t>module_repeats</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>partner_id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>partner_organisations</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -6229,12 +5289,12 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>ორგანიზაცია ვერ იშლება, თუ სტუდენტია</t>
+          <t>ხელახლა გავლა სტუდენტზე</t>
         </is>
       </c>
     </row>
@@ -6246,27 +5306,27 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>T-29</t>
+          <t>T-34</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>practice_placements</t>
+          <t>module_repeats</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>partner_teacher_id</t>
+          <t>module_instance_id</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>T-15</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>partner_teachers</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -6281,7 +5341,7 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>მასწავლებელი უნდა იყოს იმავე ორგანიზაციიდან (CHECK)</t>
+          <t>ხელახლა გავლა მოდულზე</t>
         </is>
       </c>
     </row>
@@ -6293,27 +5353,27 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>T-30</t>
+          <t>T-34</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>attendance</t>
+          <t>module_repeats</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>intake_module_id</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>module_sessions</t>
+          <t>intake_modules</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
@@ -6323,12 +5383,12 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>დასწრება საათზე</t>
+          <t>მოდულის განაწილება</t>
         </is>
       </c>
     </row>
@@ -6340,27 +5400,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>T-30</t>
+          <t>T-34</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>attendance</t>
+          <t>module_repeats</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>failed_in_group_id</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -6370,12 +5430,12 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>სტუდენტის დასწრება</t>
+          <t>საკუთარი ჯგუფი</t>
         </is>
       </c>
     </row>
@@ -6387,27 +5447,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>T-31</t>
+          <t>T-34</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>session_outcomes</t>
+          <t>module_repeats</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>repeat_with_group_id</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>module_sessions</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -6417,12 +5477,12 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>შეფასების საათი</t>
+          <t>მასპინძელი ჯგუფი — სტუდენტი ჩანს ორივეში</t>
         </is>
       </c>
     </row>
@@ -6434,27 +5494,27 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>T-31</t>
+          <t>T-40</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>session_outcomes</t>
+          <t>audit_log</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>actor_id</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -6464,12 +5524,12 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>სტუდენტის შეფასება</t>
+          <t>ჩანაწერის ავტორი</t>
         </is>
       </c>
     </row>
@@ -6481,12 +5541,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>T-32</t>
+          <t>T-42</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>outcome_results</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -6496,12 +5556,12 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
@@ -6516,7 +5576,7 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>სწავლის შედეგის ჩანაწერი</t>
+          <t>სტუდენტის გადახდები</t>
         </is>
       </c>
     </row>
@@ -6528,27 +5588,27 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>T-32</t>
+          <t>T-43</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>outcome_results</t>
+          <t>applications</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>module_instance_id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>module_instances</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -6558,12 +5618,12 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>მოდულის შედეგი</t>
+          <t>სტუდენტის განაცხადები</t>
         </is>
       </c>
     </row>
@@ -6575,27 +5635,27 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>T-32</t>
+          <t>T-45</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>outcome_results</t>
+          <t>surveys</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>outcome_id</t>
+          <t>module_instance_id</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>T-09</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>module_outcomes</t>
+          <t>module_instances</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -6605,12 +5665,12 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>SET NULL</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>კონკრეტული სწავლის შედეგი</t>
+          <t>მოდულის შეფასების გამოკითხვა</t>
         </is>
       </c>
     </row>
@@ -6622,27 +5682,27 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>T-32</t>
+          <t>T-47</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>outcome_results</t>
+          <t>clubs</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>register_id</t>
+          <t>lead_teacher_id</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>T-36</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>registers</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -6657,7 +5717,7 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>შედეგი უწყისში</t>
+          <t>კლუბის ხელმძღვანელი</t>
         </is>
       </c>
     </row>
@@ -6669,27 +5729,27 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>T-33</t>
+          <t>T-48</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>reassessments</t>
+          <t>club_events</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>club_id</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-47</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>clubs</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -6704,7 +5764,7 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>გადაბარება სტუდენტზე</t>
+          <t>კლუბის ღონისძიებები</t>
         </is>
       </c>
     </row>
@@ -6716,27 +5776,27 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>T-33</t>
+          <t>T-49</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>reassessments</t>
+          <t>club_members</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>module_instance_id</t>
+          <t>club_id</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-47</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>module_instances</t>
+          <t>clubs</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -6746,12 +5806,12 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>გადაბარება მოდულზე</t>
+          <t>კლუბის წევრობა</t>
         </is>
       </c>
     </row>
@@ -6763,27 +5823,27 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>T-33</t>
+          <t>T-49</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>reassessments</t>
+          <t>club_members</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>T-41</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>users</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -6793,1051 +5853,17 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>გადაბარება ბრძანებით</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>F-56</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>T-34</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>module_repeats</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>ხელახლა გავლა სტუდენტზე</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>F-57</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>T-34</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>module_repeats</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>failed_in_group_id</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>T-22</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>საკუთარი ჯგუფი</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>F-58</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>T-34</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>module_repeats</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>repeat_with_group_id</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>T-22</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>მასპინძელი ჯგუფი — სტუდენტი ჩანს ორივეში</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>F-59</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>T-34</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>module_repeats</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>T-41</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>ხელახლა გავლა ბრძანებით</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>F-60</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>T-35</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>assessment_instruments</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>module_instance_id</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>T-23</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>module_instances</t>
-        </is>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>ინსტრუმენტი მოდულზე</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>F-61</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>T-36</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>registers</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>module_instance_id</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>T-23</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>module_instances</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>უწყისი მოდულზე</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>F-62</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>T-36</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>registers</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>teacher_id</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>T-19</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>teachers</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>უწყისს ხელს აწერს მასწავლებელი</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>F-63</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>T-37</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>interim_assessments</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>group_id</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>T-22</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>შუალედური შეფასება ჯგუფზე</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>F-64</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>T-37</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>interim_assessments</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>T-41</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>ბრძანებით</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>F-65</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>T-38</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>individual_study_plans</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>ისგ სტუდენტზე</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>F-66</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>T-38</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>individual_study_plans</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>T-41</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>ისგ ბრძანებით</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>F-67</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>T-39</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>appeals</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>აპელაცია სტუდენტზე</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>F-68</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>T-41</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>amends_order_id</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>T-41</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H69" s="12" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>ცვლილება = ახალი ბრძანება (თვით-კავშირი)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>F-69</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>T-04</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>programs</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>T-41</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>პროგრამა მტკიცდება ბრძანებით</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>F-70</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>T-42</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>payments</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H71" s="12" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>სტუდენტის გადახდები</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>F-71</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>T-43</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>applications</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H72" s="11" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>სტუდენტის განაცხადები</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>F-72</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>T-45</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>surveys</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>module_instance_id</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>T-23</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>module_instances</t>
-        </is>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>მოდულის შეფასების გამოკითხვა</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>F-73</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>T-47</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>clubs</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>lead_teacher_id</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>T-19</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>teachers</t>
-        </is>
-      </c>
-      <c r="G74" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H74" s="11" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>კლუბის ხელმძღვანელი</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>F-74</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>T-48</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>club_events</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>club_id</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>T-47</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>clubs</t>
-        </is>
-      </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>კლუბის ღონისძიებები</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>F-75</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>T-49</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>club_members</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>club_id</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>T-47</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>clubs</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H76" s="11" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>კლუბის წევრობა</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>F-76</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>T-49</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>club_members</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H77" s="12" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
           <t>სტუდენტის წევრობა</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>F-77</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>T-40</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>audit_log</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>actor_id</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>T-18</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>admin_users</t>
-        </is>
-      </c>
-      <c r="G78" s="11" t="inlineStr">
-        <is>
-          <t>N : 1</t>
-        </is>
-      </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>ჩანაწერის ავტორი</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
+  <autoFilter ref="A1:I56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7848,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8109,120 +6135,120 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>periodEnd / weeksFor</t>
+          <t>isPrereq / dependentsOf</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>პერიოდის დასრულების თარიღი</t>
+          <t>მოდული სხვისი წინაპირობაა</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>starts_on + SUM(weeks) FROM study_period_weeks</t>
+          <t>EXISTS FROM module_prerequisites</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>გამოითვლება T-06 + T-07-დან</t>
+          <t>გადაბარების ვადის წესი</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>ხედი (გამოთვლა)</t>
+          <t>ხედი (პროექცია)</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>isPrereq / dependentsOf</t>
+          <t>repeatsInGroup</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>მოდული სხვისი წინაპირობაა</t>
+          <t>მასპინძელ ჯგუფში ხელახლა გამვლელები</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>EXISTS FROM module_prerequisites</t>
+          <t>SELECT … FROM module_repeats WHERE repeat_with_group_id = ?</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>გადაბარების ვადის წესი</t>
+          <t>ჯგუფის გვერდის ბლოკი</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>ხედი (პროექცია)</t>
+          <t>არ ინახება</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>repeatsInGroup</t>
+          <t>ბეჭდური წიგნი</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>მასპინძელ ჯგუფში ხელახლა გამვლელები</t>
+          <t>ბეჭდური კატალოგი</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>SELECT … FROM module_repeats WHERE repeat_with_group_id = ?</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ჯგუფის გვერდის ბლოკი</t>
+          <t>გარე ბიბლიოთეკის პლატფორმა — მხოლოდ ბმული</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>ხედი (პროექცია)</t>
+          <t>არ ინახება</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>usersAll</t>
+          <t>savedReports</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>ყველა მომხმარებელი ერთ სიაში</t>
+          <t>შენახული ანგარიშები</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>UNION students ∪ teachers ∪ admin_users</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>მომხმარებლების ეკრანი</t>
+          <t>ანგარიშების ეკრანი მოთხოვნით მოიხსნა, მოდელი არ არსებობს</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>არ ინახება</t>
+          <t>ლეგატური</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ბეჭდური წიგნი</t>
+          <t>moduleTemplates</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>ბეჭდური კატალოგი</t>
+          <t>მოდულის შაბლონები</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -8232,24 +6258,24 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>გარე ბიბლიოთეკის პლატფორმა — მხოლოდ ბმული</t>
+          <t>ჩანაცვლდა T-08 + T-11 + T-12-ით</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>არ ინახება</t>
+          <t>ლეგატური</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>savedReports</t>
+          <t>templateLectures</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>შენახული ანგარიშები</t>
+          <t>შაბლონის მეცადინეობები</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -8259,61 +6285,61 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>ანგარიშების ეკრანი მოთხოვნით მოიხსნა, მოდელი არ არსებობს</t>
+          <t>ჩანაცვლდა T-24-ით</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>ლეგატური</t>
+          <t>UI სარკე</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>moduleTemplates</t>
+          <t>booksData (student)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>მოდულის შაბლონები</t>
+          <t>ბიბლიოთეკის დოკუმენტები</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SELECT … FROM library_documents</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ჩანაცვლდა T-08 + T-11 + T-12-ით</t>
+          <t>სტუდენტის პორტალის პროექცია T-28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>ლეგატური</t>
+          <t>UI სარკე</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>templateLectures</t>
+          <t>myModules / moduleData</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>შაბლონის მეცადინეობები</t>
+          <t>ჩემი მოდულები</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SELECT … FROM module_instances WHERE …</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>ჩანაცვლდა T-24-ით</t>
+          <t>სტუდენტის / ლექტორის პროექცია T-23</t>
         </is>
       </c>
     </row>
@@ -8325,22 +6351,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>booksData (student)</t>
+          <t>journalStudents</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ბიბლიოთეკის დოკუმენტები</t>
+          <t>ჯგუფის სტუდენტები</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>SELECT … FROM library_documents</t>
+          <t>SELECT … FROM users WHERE role = student AND group_id = ?</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>სტუდენტის პორტალის პროექცია T-28</t>
+          <t>ლექტორის ჟურნალის პროექცია T-18</t>
         </is>
       </c>
     </row>
@@ -8352,22 +6378,22 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>myModules / moduleData</t>
+          <t>schedClasses / weekData</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>ჩემი მოდულები</t>
+          <t>ჩემი კვირის ცხრილი</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>SELECT … FROM module_instances WHERE …</t>
+          <t>SELECT … FROM schedule_entries WHERE group_id = ?</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>სტუდენტის / ლექტორის პროექცია T-23</t>
+          <t>სტუდენტის პროექცია T-27</t>
         </is>
       </c>
     </row>
@@ -8379,108 +6405,54 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>journalStudents</t>
+          <t>clubsData / newsData / jobs / surveysAll</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>ჯგუფის სტუდენტები</t>
+          <t>კონტენტის სიები</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>SELECT … FROM students WHERE group_id = ?</t>
+          <t>SELECT … FROM clubs / news / job_vacancies / surveys</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ლექტორის ჟურნალის პროექცია T-20</t>
+          <t>სტუდენტის პორტალის პროექციები</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>UI სარკე</t>
+          <t>UI მდგომარეობა</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>schedClasses / weekData</t>
+          <t>pageStack, schedPick, outF, libCatFilter</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>ჩემი კვირის ცხრილი</t>
+          <t>ნავიგაცია და ფილტრები</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>SELECT … FROM schedule_entries WHERE group_id = ?</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>სტუდენტის პროექცია T-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>UI სარკე</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>clubsData / newsData / jobs / surveysAll</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>კონტენტის სიები</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>SELECT … FROM clubs / news / job_vacancies / surveys</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>სტუდენტის პორტალის პროექციები</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>UI მდგომარეობა</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>pageStack, schedPick, outF, libCatFilter</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>ნავიგაცია და ფილტრები</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
           <t>ინტერფეისის მდგომარეობა, არ ინახება</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8491,7 +6463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8596,7 +6568,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>session_outcomes.result / outcome_results.result</t>
+          <t>session_outcomes.result</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -8813,35 +6785,39 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>assessment_direction</t>
+          <t>material_type</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>module_outcomes.direction</t>
+          <t>module_materials.type</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>survey, practical_task, practical_task_observed</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
+          <t>presentation, document, video, link, library, other</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ვიდეო მხოლოდ ჩამოტვირთვადია</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>result_source</t>
+          <t>payment_status</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>outcome_results.source</t>
+          <t>payments.status</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>assessment, formal_recognition, non_formal_recognition, mobility_transfer</t>
+          <t>paid, pending, overdue, partial</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr"/>
@@ -8849,85 +6825,45 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>material_type</t>
+          <t>application_status</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>module_materials.type / session_materials.type</t>
+          <t>applications.status</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>presentation, document, video, link, library, other</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>ვიდეო მხოლოდ ჩამოტვირთვადია</t>
-        </is>
-      </c>
+          <t>pending, approved, rejected</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>crud_op</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>payments.status</t>
+          <t>role_permissions.op</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>paid, pending, overdue, partial</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>application_status</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>applications.status</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>pending, approved, rejected</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>crud_op</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>role_permissions.op</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
           <t>c, r, u, d</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>26 რესურსი × 4 = 104 ბიტი როლზე</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8938,7 +6874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -8970,11 +6906,11 @@
         </is>
       </c>
       <c r="B2" s="15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>T-02 venues, T-08 modules, T-11 intake_modules, T-12 intake_module_weeks, T-14 partner_organisations, T-16 roles, T-28 library_documents, T-29 practice_placements, T-30 attendance, T-31 session_outcomes, T-44 news, T-45 surveys, T-46 job_vacancies, T-47 clubs</t>
+          <t>T-02 venues, T-04 programs, T-05 intakes, T-08 modules, T-11 intake_modules, T-12 intake_module_weeks, T-14 partner_organisations, T-15 partner_teachers, T-16 roles, T-22 groups, T-28 library_documents, T-29 practice_placements, T-30 attendance, T-31 session_outcomes, T-44 news, T-45 surveys, T-46 job_vacancies, T-47 clubs</t>
         </is>
       </c>
     </row>
@@ -8985,11 +6921,11 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>T-04 programs, T-07 study_period_weeks, T-10 intake_programs, T-13 module_prerequisites, T-15 partner_teachers, T-17 role_permissions, T-18 admin_users, T-19 teachers, T-20 students, T-21 student_files, T-22 groups, T-23 module_instances, T-24 module_sessions, T-25 session_materials, T-26 module_materials, T-27 schedule_entries, T-33 reassessments, T-34 module_repeats, T-40 audit_log, T-42 payments, T-43 applications, T-48 club_events, T-49 club_members</t>
+          <t>T-10 intake_programs, T-13 module_prerequisites, T-17 role_permissions, T-18 users, T-21 student_files, T-23 module_instances, T-24 module_sessions, T-26 module_materials, T-27 schedule_entries, T-33 reassessments, T-34 module_repeats, T-40 audit_log, T-41 orders, T-42 payments, T-43 applications, T-48 club_events, T-49 club_members</t>
         </is>
       </c>
     </row>
@@ -9000,11 +6936,11 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>T-01 branches, T-03 lesson_slots, T-05 intakes, T-06 study_periods, T-09 module_outcomes, T-32 outcome_results, T-35 assessment_instruments, T-36 registers, T-37 interim_assessments, T-38 individual_study_plans, T-39 appeals, T-41 orders</t>
+          <t>T-03 lesson_slots</t>
         </is>
       </c>
     </row>
@@ -9020,7 +6956,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
     </row>
@@ -9031,7 +6967,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C7" s="8" t="inlineStr"/>
     </row>
@@ -9042,7 +6978,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
     </row>
@@ -9053,7 +6989,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -9078,7 +7014,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>• ბრძანებით მართული სტატუსი — students, teachers, admin_users, groups, module_instances არ იშლება: სტატუსი იცვლება ან ჩანაწერი დეაქტივირდება (T-18, T-19, T-20, T-22, T-23)</t>
+          <t>• ბრძანებით მართული სტატუსი — users და module_instances არ იშლება: სტატუსი იცვლება ან ჩანაწერი დეაქტივირდება (T-18, T-23)</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
@@ -9096,7 +7032,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>• წარმოებული ჩანაწერი — module_sessions გენერირდება კვირეული განაწილებიდან, outcome_results იწერება შეფასების საათიდან (T-24, T-32)</t>
+          <t>• წარმოებული ჩანაწერი — module_sessions გენერირდება მიღების მოდულის კვირეული განაწილებიდან, ხელით არ იქმნება (T-24)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr"/>
@@ -9105,7 +7041,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>• პროცესი სისტემის გარეთ — assessment_instruments ვალიდაცია და registers ხელმოწერა სისტემის გარეთ ხდება (T-35, T-36)</t>
+          <t>• წინასწარ განსაზღვრული საცნობარო — lesson_slots ფიქსირებულია (T-03)</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr"/>
@@ -9114,7 +7050,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>• წინასწარ განსაზღვრული საცნობარო — intakes, lesson_slots, branches ფიქსირებულია (T-01, T-03, T-05)</t>
+          <t>• რედაქტირების ნაცვლად წაშლა + ხელახლა დამატება — intake_programs, module_prerequisites, partner_teachers, student_files, module_materials, schedule_entries, club_events, club_members (T-10, T-13, T-15, T-21, T-26, T-27, T-48, T-49)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
@@ -9123,7 +7059,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>• ინტერფეისი მოთხოვნით მოიხსნა — study_periods, study_period_weeks, module_outcomes, registers, interim_assessments, individual_study_plans, appeals (T-06, T-07, T-09, T-36, T-37, T-38, T-39)</t>
+          <t>• ფინანსური და ისტორიული ჩანაწერი — payments, applications, reassessments, module_repeats არ იშლება (T-33, T-34, T-42, T-43)</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr"/>
@@ -9132,7 +7068,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>• რედაქტირების ნაცვლად წაშლა + ხელახლა დამატება — intake_programs, module_prerequisites, partner_teachers, student_files, session_materials, module_materials, schedule_entries, club_events, club_members (T-10, T-13, T-15, T-21, T-25, T-26, T-27, T-48, T-49)</t>
+          <t>• programs — რედაქტირება მოთხოვნით ამოღებულია, დარჩა დამატება და წაშლა (T-04)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr"/>
@@ -9141,32 +7077,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>• ფინანსური და ისტორიული ჩანაწერი — payments, applications, reassessments, module_repeats არ იშლება (T-33, T-34, T-42, T-43)</t>
+          <t>• role_permissions — მატრიცა როლთან ერთად არსებობს, ცალკე ჩანაწერი არ იქმნება და არ იშლება (T-17)</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr"/>
       <c r="C19" s="8" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>• programs — რედაქტირება მოთხოვნით ამოღებულია, დარჩა დამატება და წაშლა (T-04)</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>• role_permissions — მატრიცა როლთან ერთად არსებობს, ცალკე ჩანაწერი არ იქმნება და არ იშლება (T-17)</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C21"/>
+  <autoFilter ref="A1:C19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/BMA_DB_Tables_CRUD.xlsx
+++ b/BMA_DB_Tables_CRUD.xlsx
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>no, date, index (01 | 02), subject, file_url</t>
+          <t>no, date, index (general_01 | student_02), subject, eflow, e_sign, p_sign, file_url</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>students.status</t>
+          <t>users.status (role = student)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>იცვლება მხოლოდ ბრძანებით</t>
+          <t>შეჩერების და შეწყვეტის მიზეზი ცალკე ჩამონათვალია</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>teachers.status</t>
+          <t>users.status (role = teacher)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6657,10 +6657,14 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>higher_vocational, secondary_vocational</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr"/>
+          <t>basic_vocational, secondary_vocational, higher_vocational, preparation, retraining</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>PROGRAM_TYPE_LBL — საბაზო / საშუალო / უმაღლესი პროფესიული, მოსამზადებელი, გადამზადება</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -6670,7 +6674,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>teachers.implementer_type</t>
+          <t>users.implementer_type (role = teacher)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -6680,7 +6684,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>რეგისტრირდება მხოლოდ პროფ. განათლების მასწავლებელი</t>
+          <t>ერთადერთი მნიშვნელობა — რეგისტრირდება მხოლოდ პროფესიული განათლების მასწავლებელი</t>
         </is>
       </c>
     </row>
@@ -6773,12 +6777,12 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>01 (ზოგადი), 02 (სტუდენტი)</t>
+          <t>general_01 (01 — ზოგადი), student_02 (02 — სტუდენტი)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>ნომერი — ციფრები, თანმიმდევრობით კალენდარულ წელში</t>
+          <t>რეგისტრის ინდექსი — ბრძანების ნომერი კალენდარულ წელში თანმიმდევრობითია</t>
         </is>
       </c>
     </row>

--- a/BMA_DB_Tables_CRUD.xlsx
+++ b/BMA_DB_Tables_CRUD.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ცხრილები'!$A$1:$N$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'კავშირები (FK)'!$A$1:$I$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'გამოტანილი — ხედები'!$A$1:$E$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ჩამონათვალები (enum)'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ჩამონათვალები (enum)'!$A$1:$D$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CRUD მიმოხილვა'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'ლეგენდა'!$A$1:$B$18</definedName>
   </definedNames>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>resource (26), op (c|r|u|d), allowed</t>
+          <t>resource (23), op (c|r|u|d), allowed</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>no, date, index (general_01 | student_02), subject, eflow, e_sign, p_sign, file_url</t>
+          <t>no, date, subject, eflow, e_sign, p_sign, file_url</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>ბრძანება მხოლოდ აიტვირთება და იკითხება — სისტემაში სხვა ჩანაწერს არ ებმევა, არაფრის წინაპირობა არ არის</t>
+          <t>რეგისტრში ქვეყნდება მხოლოდ ზოგადი ბრძანებები; მხოლოდ აიტვირთება და იკითხება — სისტემაში სხვა ჩანაწერს არ ებმევა, არაფრის წინაპირობა არ არის</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6767,61 +6767,57 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>order_index</t>
+          <t>material_type</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>orders.index</t>
+          <t>module_materials.type</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>general_01 (01 — ზოგადი), student_02 (02 — სტუდენტი)</t>
+          <t>presentation, document, video, link, library, other</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>რეგისტრის ინდექსი — ბრძანების ნომერი კალენდარულ წელში თანმიმდევრობითია</t>
+          <t>ვიდეო მხოლოდ ჩამოტვირთვადია</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>material_type</t>
+          <t>payment_status</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>module_materials.type</t>
+          <t>payments.status</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>presentation, document, video, link, library, other</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>ვიდეო მხოლოდ ჩამოტვირთვადია</t>
-        </is>
-      </c>
+          <t>paid, pending, overdue, partial</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>application_status</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>payments.status</t>
+          <t>applications.status</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>paid, pending, overdue, partial</t>
+          <t>pending, approved, rejected</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr"/>
@@ -6829,45 +6825,27 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>application_status</t>
+          <t>crud_op</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>applications.status</t>
+          <t>role_permissions.op</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>pending, approved, rejected</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>crud_op</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>role_permissions.op</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
           <t>c, r, u, d</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>26 რესურსი × 4 = 104 ბიტი როლზე</t>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>23 რესურსი × 4 = 92 ბიტი როლზე</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19"/>
+  <autoFilter ref="A1:D18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6982,7 +6960,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
     </row>

--- a/BMA_DB_Tables_CRUD.xlsx
+++ b/BMA_DB_Tables_CRUD.xlsx
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>no, date, subject, eflow, e_sign, p_sign, file_url</t>
+          <t>no, date, subject, eflow, amends_order_no, file_url</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
